--- a/Program/CAISO-API/Month_Agg_Clear/CAISO_NG_2025_11.xlsx
+++ b/Program/CAISO-API/Month_Agg_Clear/CAISO_NG_2025_11.xlsx
@@ -184,8 +184,8 @@
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Hans" typeface="SimSun"/>
+        <a:font script="Hant" typeface="PMingLiU"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -218,8 +218,8 @@
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Hans" typeface="SimSun"/>
+        <a:font script="Hant" typeface="PMingLiU"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
